--- a/Excel/MineConfig.xlsx
+++ b/Excel/MineConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="80">
   <si>
     <t>#</t>
   </si>
@@ -213,6 +213,36 @@
   </si>
   <si>
     <t>减伤</t>
+  </si>
+  <si>
+    <t>物伤石</t>
+  </si>
+  <si>
+    <t>物伤倍率</t>
+  </si>
+  <si>
+    <t>法伤石</t>
+  </si>
+  <si>
+    <t>法伤倍率</t>
+  </si>
+  <si>
+    <t>道伤石</t>
+  </si>
+  <si>
+    <t>道伤倍率</t>
+  </si>
+  <si>
+    <t>韧性石</t>
+  </si>
+  <si>
+    <t>韧性倍率</t>
+  </si>
+  <si>
+    <t>破韧石</t>
+  </si>
+  <si>
+    <t>破韧倍率</t>
   </si>
   <si>
     <t>矿石之精</t>
@@ -1201,7 +1231,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:I35"/>
+  <dimension ref="C1:I41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1212,12 +1242,12 @@
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="9:9">
+    <row r="1" customHeight="1" spans="3:9">
       <c r="I1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="9:9">
+    <row r="2" customHeight="1" spans="3:9">
       <c r="I2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1891,22 +1921,22 @@
     </row>
     <row r="32" customHeight="1" spans="3:9">
       <c r="C32" s="1">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
       </c>
       <c r="E32" s="1">
+        <v>50</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G32" s="1">
         <v>10</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G32" s="1">
-        <v>6</v>
-      </c>
       <c r="H32" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>63</v>
@@ -1914,22 +1944,22 @@
     </row>
     <row r="33" customHeight="1" spans="3:9">
       <c r="C33" s="1">
-        <v>102</v>
+        <v>28</v>
       </c>
       <c r="D33" s="1">
         <v>1</v>
       </c>
       <c r="E33" s="1">
-        <v>20</v>
-      </c>
-      <c r="F33" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G33" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H33" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>65</v>
@@ -1937,22 +1967,22 @@
     </row>
     <row r="34" customHeight="1" spans="3:9">
       <c r="C34" s="1">
-        <v>103</v>
+        <v>29</v>
       </c>
       <c r="D34" s="1">
         <v>1</v>
       </c>
       <c r="E34" s="1">
-        <v>30</v>
-      </c>
-      <c r="F34" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G34" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H34" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>67</v>
@@ -1960,25 +1990,143 @@
     </row>
     <row r="35" customHeight="1" spans="3:9">
       <c r="C35" s="1">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="D35" s="1">
         <v>1</v>
       </c>
       <c r="E35" s="1">
-        <v>40</v>
-      </c>
-      <c r="F35" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>68</v>
       </c>
       <c r="G35" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H35" s="1">
         <v>0</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:9">
+      <c r="C36" s="1">
+        <v>31</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1</v>
+      </c>
+      <c r="E36" s="1">
+        <v>70</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G36" s="1">
+        <v>10</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:9">
+      <c r="F37" s="3"/>
+    </row>
+    <row r="38" customHeight="1" spans="3:9">
+      <c r="C38" s="1">
+        <v>101</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1</v>
+      </c>
+      <c r="E38" s="1">
+        <v>10</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G38" s="1">
+        <v>6</v>
+      </c>
+      <c r="H38" s="1">
+        <v>6</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:9">
+      <c r="C39" s="1">
+        <v>102</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1</v>
+      </c>
+      <c r="E39" s="1">
+        <v>20</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G39" s="1">
+        <v>6</v>
+      </c>
+      <c r="H39" s="1">
+        <v>4</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:9">
+      <c r="C40" s="1">
+        <v>103</v>
+      </c>
+      <c r="D40" s="1">
+        <v>1</v>
+      </c>
+      <c r="E40" s="1">
+        <v>30</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G40" s="1">
+        <v>6</v>
+      </c>
+      <c r="H40" s="1">
+        <v>2</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:9">
+      <c r="C41" s="1">
+        <v>104</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1</v>
+      </c>
+      <c r="E41" s="1">
+        <v>40</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G41" s="1">
+        <v>3</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MineConfig.xlsx
+++ b/Excel/MineConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
   <si>
     <t>#</t>
   </si>
@@ -243,6 +243,42 @@
   </si>
   <si>
     <t>破韧倍率</t>
+  </si>
+  <si>
+    <t>极·墨水晶</t>
+  </si>
+  <si>
+    <t>极·蓝水晶</t>
+  </si>
+  <si>
+    <t>极·方解石</t>
+  </si>
+  <si>
+    <t>物攻倍率</t>
+  </si>
+  <si>
+    <t>极·橄榄石</t>
+  </si>
+  <si>
+    <t>极·星叶石</t>
+  </si>
+  <si>
+    <t>极·韧性石</t>
+  </si>
+  <si>
+    <t>极·物伤石</t>
+  </si>
+  <si>
+    <t>极·法伤石</t>
+  </si>
+  <si>
+    <t>极·道伤石</t>
+  </si>
+  <si>
+    <t>极·黑曜石</t>
+  </si>
+  <si>
+    <t>极·破韧石</t>
   </si>
   <si>
     <t>矿石之精</t>
@@ -1231,7 +1267,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:I41"/>
+  <dimension ref="C1:I56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -2035,49 +2071,69 @@
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:9">
-      <c r="F37" s="3"/>
+      <c r="C37" s="1">
+        <v>32</v>
+      </c>
+      <c r="D37" s="1">
+        <v>1</v>
+      </c>
+      <c r="E37" s="1">
+        <v>80</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G37" s="1">
+        <v>5</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="38" customHeight="1" spans="3:9">
       <c r="C38" s="1">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="D38" s="1">
         <v>1</v>
       </c>
       <c r="E38" s="1">
-        <v>10</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="G38" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H38" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:9">
       <c r="C39" s="1">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="D39" s="1">
         <v>1</v>
       </c>
       <c r="E39" s="1">
-        <v>20</v>
-      </c>
-      <c r="F39" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>74</v>
       </c>
       <c r="G39" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H39" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>75</v>
@@ -2085,48 +2141,293 @@
     </row>
     <row r="40" customHeight="1" spans="3:9">
       <c r="C40" s="1">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="D40" s="1">
         <v>1</v>
       </c>
       <c r="E40" s="1">
-        <v>30</v>
-      </c>
-      <c r="F40" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>76</v>
       </c>
       <c r="G40" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H40" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:9">
       <c r="C41" s="1">
+        <v>36</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1</v>
+      </c>
+      <c r="E41" s="1">
+        <v>100</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G41" s="1">
+        <v>5</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:9">
+      <c r="C42" s="1">
+        <v>37</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1</v>
+      </c>
+      <c r="E42" s="1">
+        <v>110</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G42" s="1">
+        <v>5</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:9">
+      <c r="C43" s="1">
+        <v>38</v>
+      </c>
+      <c r="D43" s="1">
+        <v>1</v>
+      </c>
+      <c r="E43" s="1">
+        <v>120</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G43" s="1">
+        <v>5</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:9">
+      <c r="C44" s="1">
+        <v>39</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1</v>
+      </c>
+      <c r="E44" s="1">
+        <v>120</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G44" s="1">
+        <v>5</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:9">
+      <c r="C45" s="1">
+        <v>40</v>
+      </c>
+      <c r="D45" s="1">
+        <v>1</v>
+      </c>
+      <c r="E45" s="1">
+        <v>120</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G45" s="1">
+        <v>5</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:9">
+      <c r="C46" s="1">
+        <v>41</v>
+      </c>
+      <c r="D46" s="1">
+        <v>1</v>
+      </c>
+      <c r="E46" s="1">
+        <v>130</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G46" s="1">
+        <v>5</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:9">
+      <c r="C47" s="1">
+        <v>42</v>
+      </c>
+      <c r="D47" s="1">
+        <v>1</v>
+      </c>
+      <c r="E47" s="1">
+        <v>140</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G47" s="1">
+        <v>5</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:9">
+      <c r="F48" s="3"/>
+    </row>
+    <row r="49" customHeight="1" spans="3:9">
+      <c r="F49" s="3"/>
+    </row>
+    <row r="50" customHeight="1" spans="3:9">
+      <c r="F50" s="3"/>
+    </row>
+    <row r="51" customHeight="1" spans="3:9">
+      <c r="F51" s="3"/>
+    </row>
+    <row r="52" customHeight="1" spans="3:9">
+      <c r="F52" s="3"/>
+    </row>
+    <row r="53" customHeight="1" spans="3:9">
+      <c r="C53" s="1">
+        <v>101</v>
+      </c>
+      <c r="D53" s="1">
+        <v>1</v>
+      </c>
+      <c r="E53" s="1">
+        <v>10</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G53" s="1">
+        <v>6</v>
+      </c>
+      <c r="H53" s="1">
+        <v>6</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:9">
+      <c r="C54" s="1">
+        <v>102</v>
+      </c>
+      <c r="D54" s="1">
+        <v>1</v>
+      </c>
+      <c r="E54" s="1">
+        <v>20</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G54" s="1">
+        <v>6</v>
+      </c>
+      <c r="H54" s="1">
+        <v>4</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:9">
+      <c r="C55" s="1">
+        <v>103</v>
+      </c>
+      <c r="D55" s="1">
+        <v>1</v>
+      </c>
+      <c r="E55" s="1">
+        <v>30</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G55" s="1">
+        <v>6</v>
+      </c>
+      <c r="H55" s="1">
+        <v>2</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:9">
+      <c r="C56" s="1">
         <v>104</v>
       </c>
-      <c r="D41" s="1">
-        <v>1</v>
-      </c>
-      <c r="E41" s="1">
+      <c r="D56" s="1">
+        <v>1</v>
+      </c>
+      <c r="E56" s="1">
         <v>40</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G41" s="1">
+      <c r="F56" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G56" s="1">
         <v>3</v>
       </c>
-      <c r="H41" s="1">
-        <v>0</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>79</v>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
